--- a/data/file_generation/input/data_70/各月按部门薪酬发放明细.xlsx
+++ b/data/file_generation/input/data_70/各月按部门薪酬发放明细.xlsx
@@ -18208,26 +18208,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6F2FBCF-2BA9-4DC3-8CA4-E789EAB8AAE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91C4C0DF-E98A-48DE-B0CB-5D45BE776F62}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B07F6953-7C20-4613-9C54-E2916ACFB9DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{909931DF-D46E-4115-AF51-D2E79A406B97}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAEDC169-AAA9-4016-A6C2-5CBEC343744B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B454EEF-E692-40A2-B490-80114BD502CD}"/>
 </file>